--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/02_Produktion_Medien/03_Medien_und_Geraeteinventar.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/02_Produktion_Medien/03_Medien_und_Geraeteinventar.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physische_Medien" sheetId="1" r:id="R7edcbf2df5a541ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nichtkoerperliche_Kopien" sheetId="2" r:id="Rdab107783d494be6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pruefpunkte" sheetId="3" r:id="R9a2111579e484f2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physische_Medien" sheetId="1" r:id="Ra488e60be06a4f5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nichtkoerperliche_Kopien" sheetId="2" r:id="R5c88146cfe8f4c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pruefpunkte" sheetId="3" r:id="R8e9e7cb8f5b549d8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/02_Produktion_Medien/03_Medien_und_Geraeteinventar.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/02_Produktion_Medien/03_Medien_und_Geraeteinventar.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physische_Medien" sheetId="1" r:id="Ra488e60be06a4f5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nichtkoerperliche_Kopien" sheetId="2" r:id="R5c88146cfe8f4c8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pruefpunkte" sheetId="3" r:id="R8e9e7cb8f5b549d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physische_Medien" sheetId="1" r:id="Rab1267cbf19a4fcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nichtkoerperliche_Kopien" sheetId="2" r:id="R2101f468bc8d4441"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pruefpunkte" sheetId="3" r:id="Re79771b4d6594b74"/>
   </x:sheets>
 </x:workbook>
 </file>
